--- a/doc/5、开发文档/DFDL33-SH8619软硬件接口文档.xlsx
+++ b/doc/5、开发文档/DFDL33-SH8619软硬件接口文档.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Project\SVN\DFDL33-SH8619\doc\5、开发文档\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77DE867F-BCA1-4C8A-9631-FBA9DCD266CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8079BD54-D37C-481F-B3D5-67EBB56895A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="139">
   <si>
     <t>接口</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -559,6 +559,18 @@
   </si>
   <si>
     <t>PB11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>北向串口</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>南向485</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>北向串口485</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1558,7 +1570,9 @@
       <c r="D8" s="59" t="s">
         <v>134</v>
       </c>
-      <c r="E8" s="62"/>
+      <c r="E8" s="62" t="s">
+        <v>138</v>
+      </c>
       <c r="F8" s="58"/>
       <c r="G8" s="7"/>
     </row>
@@ -1648,7 +1662,9 @@
       <c r="D14" s="59" t="s">
         <v>121</v>
       </c>
-      <c r="E14" s="62"/>
+      <c r="E14" s="62" t="s">
+        <v>137</v>
+      </c>
       <c r="F14" s="58"/>
       <c r="G14" s="7"/>
     </row>
@@ -1708,7 +1724,9 @@
       <c r="D18" s="59" t="s">
         <v>130</v>
       </c>
-      <c r="E18" s="62"/>
+      <c r="E18" s="62" t="s">
+        <v>136</v>
+      </c>
       <c r="F18" s="58"/>
       <c r="G18" s="7"/>
     </row>
